--- a/mapping/SB_DWH/Mapping_FCT_RLOS_COLLATERAL.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_COLLATERAL.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,8 +167,16 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -239,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,7 +408,10 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -713,11 +724,11 @@
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
     <col width="19" customWidth="1" style="19" min="2" max="2"/>
     <col width="30.6640625" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="36.6640625" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
-    <col width="59.5" customWidth="1" style="19" min="5" max="5"/>
-    <col width="59.1640625" customWidth="1" style="16" min="6" max="6"/>
-    <col width="59.1640625" customWidth="1" style="19" min="7" max="16384"/>
-    <col width="59.1640625" customWidth="1" min="8" max="8"/>
+    <col width="69.1640625" customWidth="1" style="16" min="4" max="4"/>
+    <col width="90.1640625" customWidth="1" style="19" min="5" max="5"/>
+    <col width="90.1640625" customWidth="1" style="16" min="6" max="6"/>
+    <col width="90.1640625" customWidth="1" style="19" min="7" max="16384"/>
+    <col width="90.1640625" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -936,7 +947,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="51" customHeight="1">
+    <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -950,7 +961,7 @@
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -966,33 +977,33 @@
           <t>Ngày dữ liệu</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>PK — Driving: UNION 4 khối nguồn không driving table chung (NG_SB_RLOS_COL_REALESTATE/COL_TRANSPORT/COL_VALPAPER/COL_OTHER). Ảnh chụp đầy đủ theo ngày (quy trình A2), áp dụng chung cho mọi khối nguồn</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>v_batch_date</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="31" t="inlineStr">
         <is>
           <t>v_batch_date</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="31" t="inlineStr">
         <is>
           <t>v_batch_date</t>
         </is>
       </c>
-      <c r="H17" s="28" t="inlineStr">
+      <c r="H17" s="31" t="inlineStr">
         <is>
           <t>v_batch_date</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="210" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>COLLATERAL_BK</t>
@@ -1008,33 +1019,33 @@
           <t>Khóa nghiệp vụ</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="54" t="inlineStr">
         <is>
           <t>Khóa nghiệp vụ của dòng tài sản — nguồn không khai khóa CDC nên phải hash. Hash trên toàn bộ cột non-CLOB của khối nguồn tương ứng theo RLOS - Metadata.xlsx, cộng tên bảng nguồn để 4 khối không đụng khóa</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>STANDARD_HASH(TRIM(NVL(A.WI_NAME,'&lt;NULL&gt;')) || TRIM(NVL(A.PROPERTY,'&lt;NULL&gt;')) || TRIM(NVL(A.NO_CERTI,'&lt;NULL&gt;')) || TRIM(NVL(A.OWNER,'&lt;NULL&gt;')) || TRIM(NVL(A.OWNER1,'&lt;NULL&gt;')) || TRIM(NVL(A.REL_CUSTOMER,'&lt;NULL&gt;')) || TRIM(NVL(A.REL_CUSTOMER1,'&lt;NULL&gt;')) || TRIM(NVL(A.REL_TYPE,'&lt;NULL&gt;')) || TRIM(NVL(TO_CHAR(A.ISSUE_DATE,'YYYYMMDD'),'&lt;NULL&gt;')) || TRIM(NVL(A.ISSUE_PLACE,'&lt;NULL&gt;')) || TRIM(NVL(A.AREA,'&lt;NULL&gt;')) || TRIM(NVL(A.BUILDING,'&lt;NULL&gt;')) || TRIM(NVL(A.PRICING_VALUE,'&lt;NULL&gt;')) || TRIM(NVL(A.PRICING_UNIT,'&lt;NULL&gt;')) || TRIM(NVL(TO_CHAR(A.PRICING_DATE,'YYYYMMDD'),'&lt;NULL&gt;')) || TRIM(NVL(TO_CHAR(A.LOANRATE),'&lt;NULL&gt;')) || TRIM(NVL(A.REMARKS,'&lt;NULL&gt;')) || TRIM(NVL(A.ADDRESS,'&lt;NULL&gt;')) || TRIM(NVL(A.HOUSE_TYPE,'&lt;NULL&gt;')) || TRIM(NVL(A.USING_PURPOSE,'&lt;NULL&gt;')) || TRIM(NVL(A.SECURITY_VALUE,'&lt;NULL&gt;')), 'MD5')</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>STANDARD_HASH(TRIM(NVL(A.WI_NAME,'&lt;NULL&gt;')) || TRIM(NVL(A.PROPERTY,'&lt;NULL&gt;')) || TRIM(NVL(A.OWNER,'&lt;NULL&gt;')) || TRIM(NVL(A.RELATION_CUSTOMER,'&lt;NULL&gt;')) || TRIM(NVL(A.TYPE_VEHICLE,'&lt;NULL&gt;')) || TRIM(NVL(A.BRAND,'&lt;NULL&gt;')) || TRIM(NVL(A.CONTROL_POSTER,'&lt;NULL&gt;')) || TRIM(NVL(A.PURCHASE_CONTRACT,'&lt;NULL&gt;')) || TRIM(NVL(A.INVOICE,'&lt;NULL&gt;')) || TRIM(NVL(A.SITUATION,'&lt;NULL&gt;')) || TRIM(NVL(A.PRICINGVALUE,'&lt;NULL&gt;')) || TRIM(NVL(A.PRICINGUNIT,'&lt;NULL&gt;')) || TRIM(NVL(TO_CHAR(A.PRICINGDATE,'YYYYMMDD'),'&lt;NULL&gt;')) || TRIM(NVL(TO_CHAR(A.LOANRATE),'&lt;NULL&gt;')) || TRIM(NVL(A.SECURITY_VALUE,'&lt;NULL&gt;')), 'MD5')</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="31" t="inlineStr">
         <is>
           <t>STANDARD_HASH(TRIM(NVL(A.WI_NAME,'&lt;NULL&gt;')) || TRIM(NVL(A.PROPERTY,'&lt;NULL&gt;')) || TRIM(NVL(A.OWNER,'&lt;NULL&gt;')) || TRIM(NVL(A.RELATION_CUSTOMER,'&lt;NULL&gt;')) || TRIM(NVL(A.TYPE1,'&lt;NULL&gt;')) || TRIM(NVL(A.ISSUER,'&lt;NULL&gt;')) || TRIM(NVL(A.NUMBERSIGN,'&lt;NULL&gt;')) || TRIM(NVL(A.PARVALUE,'&lt;NULL&gt;')) || TRIM(NVL(A.CURRENCY,'&lt;NULL&gt;')) || TRIM(NVL(A.PRICINGVALUE,'&lt;NULL&gt;')) || TRIM(NVL(TO_CHAR(A.LOANRATE),'&lt;NULL&gt;')) || TRIM(NVL(A.SECURITY_VALUE,'&lt;NULL&gt;')), 'MD5')</t>
         </is>
       </c>
-      <c r="H18" s="28" t="inlineStr">
+      <c r="H18" s="31" t="inlineStr">
         <is>
           <t>STANDARD_HASH(TRIM(NVL(A.WI_NAME,'&lt;NULL&gt;')) || TRIM(NVL(A.PROPERTY,'&lt;NULL&gt;')) || TRIM(NVL(A.OWNER,'&lt;NULL&gt;')) || TRIM(NVL(A.RELATION_CUSTOMER,'&lt;NULL&gt;')) || TRIM(NVL(A.DESCRIBE,'&lt;NULL&gt;')) || TRIM(NVL(A.PRICINGVALUE,'&lt;NULL&gt;')) || TRIM(NVL(TO_CHAR(A.LOANRATE),'&lt;NULL&gt;')) || TRIM(NVL(A.SECURITY_VALUE,'&lt;NULL&gt;')), 'MD5')</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
@@ -1050,33 +1061,33 @@
           <t>Khóa tới hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>Khóa ngoại — tra DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>Khóa ngoại — tra DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>B.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="31" t="inlineStr">
         <is>
           <t>B.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G19" s="31" t="inlineStr">
         <is>
           <t>B.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="H19" s="28" t="inlineStr">
+      <c r="H19" s="31" t="inlineStr">
         <is>
           <t>B.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="20">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>WI_NAME</t>
@@ -1092,33 +1103,33 @@
           <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng RLOS</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr">
+      <c r="G20" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="H20" s="28" t="inlineStr">
+      <c r="H20" s="31" t="inlineStr">
         <is>
           <t>DISTINCT A.WI_NAME</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
           <t>COLLATERAL_TYPE_CODE</t>
@@ -1134,33 +1145,33 @@
           <t>Mã loại tài sản bảo đảm</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
         <is>
           <t>Nhãn phân loại nguồn của tài sản bảo đảm — gán cố định theo bảng grid sinh ra dòng đó. Dùng để CASE chọn đúng cột chi tiết khi dựng TYPES_OF_COLLATERALS. Không phải dữ liệu mô tả tài sản</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>'REALESTATE'</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="31" t="inlineStr">
         <is>
           <t>'TRANSPORT'</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="G21" s="31" t="inlineStr">
         <is>
           <t>'VALPAPER'</t>
         </is>
       </c>
-      <c r="H21" s="28" t="inlineStr">
+      <c r="H21" s="31" t="inlineStr">
         <is>
           <t>'OTHER'</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22" ht="105" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
           <t>CERTIFICATE_NO</t>
@@ -1176,33 +1187,33 @@
           <t>Số giấy chứng nhận tài sản</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="54" t="inlineStr">
         <is>
           <t>Số giấy chứng nhận tài sản. Phục vụ BC1.GCN_REAL_ESTATE (REALESTATE), BC1.GCN_OTHER (3 khối còn lại) — tách khi dựng BC1 bằng WHERE COLLATERAL_TYPE_CODE. VALPAPER lấy trực tiếp NUMBERSIGN của chính bảng (không qua CERTIGRD); TRANSPORT/OTHER JOIN NG_SB_RLOS_COLL_CERTIGRD (dedup theo WI_NAME+OWNER+RELATIONSHIP, lấy bản ghi mới nhất theo RECID)</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>A.NO_CERTI</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="31" t="inlineStr">
         <is>
           <t>C.CERTIFICATENO</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr">
+      <c r="G22" s="31" t="inlineStr">
         <is>
           <t>A.NUMBERSIGN</t>
         </is>
       </c>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="H22" s="31" t="inlineStr">
         <is>
           <t>C.CERTIFICATENO</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
@@ -1218,27 +1229,27 @@
           <t>Mô tả tài sản bảo đảm</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="54" t="inlineStr">
         <is>
           <t>Mô tả tài sản bảo đảm (BC3.DESCRIPTION). Đúng nguyên văn SRS BC3, REALESTATE không dùng REMARKS</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>A.NO_CERTI || ', ' || A.USING_PURPOSE</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="31" t="inlineStr">
         <is>
           <t>A.BRAND || ', ' || A.CONTROL_POSTER</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr">
+      <c r="G23" s="31" t="inlineStr">
         <is>
           <t>A.NUMBERSIGN</t>
         </is>
       </c>
-      <c r="H23" s="28" t="inlineStr">
+      <c r="H23" s="31" t="inlineStr">
         <is>
           <t>A.DESCRIBE</t>
         </is>
@@ -1260,33 +1271,33 @@
           <t>Chủ sở hữu tài sản</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="54" t="inlineStr">
         <is>
           <t>Chủ sở hữu tài sản (cũng là BC1.OWNERSHIP)</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.OWNER</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="31" t="inlineStr">
         <is>
           <t>A.OWNER</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="G24" s="31" t="inlineStr">
         <is>
           <t>A.OWNER</t>
         </is>
       </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="H24" s="31" t="inlineStr">
         <is>
           <t>A.OWNER</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
           <t>REL_TO_CUSTOMER</t>
@@ -1302,33 +1313,33 @@
           <t>Quan hệ chủ tài sản-khách hàng</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
         <is>
           <t>Quan hệ giữa chủ tài sản và khách hàng (BC1.TSBD_RELATIONSHIP). REALESTATE dùng tên cột nguồn REL_CUSTOMER, 3 khối còn lại dùng RELATION_CUSTOMER (đã xác nhận qua RLOS - Metadata.xlsx)</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A.REL_CUSTOMER</t>
         </is>
       </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="F25" s="31" t="inlineStr">
         <is>
           <t>A.RELATION_CUSTOMER</t>
         </is>
       </c>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G25" s="31" t="inlineStr">
         <is>
           <t>A.RELATION_CUSTOMER</t>
         </is>
       </c>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="H25" s="31" t="inlineStr">
         <is>
           <t>A.RELATION_CUSTOMER</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
           <t>USING_PURPOSE</t>
@@ -1344,33 +1355,33 @@
           <t>Mục đích sử dụng BĐS</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
         <is>
           <t>Mục đích sử dụng của bất động sản. Chỉ có ở khối REALESTATE — NULL ở 3 khối còn lại</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>A.USING_PURPOSE</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="F26" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G26" s="28" t="inlineStr">
+      <c r="G26" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="H26" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="75" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
           <t>APPRAISED_VALUE</t>
@@ -1386,33 +1397,33 @@
           <t>Giá trị định giá tài sản</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D27" s="54" t="inlineStr">
         <is>
           <t>Giá trị định giá của tài sản. Dữ liệu mẫu thực tế hỗn hợp: phần lớn số nguyên thuần không dấu phân cách, một số có dấu phẩy ngăn nghìn + dấu chấm thập phân kiểu Anh-Mỹ, một số text thuần không phải số → NULL. Công thức: bỏ dấu phẩy ngăn nghìn, giữ dấu chấm, TO_NUMBER với DEFAULT NULL ON CONVERSION ERROR</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>TO_NUMBER(REPLACE(A.PRICING_VALUE, ',', '') DEFAULT NULL ON CONVERSION ERROR)</t>
         </is>
       </c>
-      <c r="F27" s="28" t="inlineStr">
+      <c r="F27" s="31" t="inlineStr">
         <is>
           <t>TO_NUMBER(REPLACE(A.PRICINGVALUE, ',', '') DEFAULT NULL ON CONVERSION ERROR)</t>
         </is>
       </c>
-      <c r="G27" s="28" t="inlineStr">
+      <c r="G27" s="31" t="inlineStr">
         <is>
           <t>TO_NUMBER(REPLACE(A.PRICINGVALUE, ',', '') DEFAULT NULL ON CONVERSION ERROR)</t>
         </is>
       </c>
-      <c r="H27" s="28" t="inlineStr">
+      <c r="H27" s="31" t="inlineStr">
         <is>
           <t>TO_NUMBER(REPLACE(A.PRICINGVALUE, ',', '') DEFAULT NULL ON CONVERSION ERROR)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
           <t>LOAN_RATE_LTV</t>
@@ -1428,33 +1439,33 @@
           <t>Tỷ lệ cho vay/TSBĐ</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Tỷ lệ cho vay trên giá trị tài sản, đơn vị phần trăm — cùng quy tắc ép kiểu với APPRAISED_VALUE</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>TO_NUMBER(REPLACE(A.LOANRATE, ',', '') DEFAULT NULL ON CONVERSION ERROR)</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="31" t="inlineStr">
         <is>
           <t>TO_NUMBER(REPLACE(A.LOANRATE, ',', '') DEFAULT NULL ON CONVERSION ERROR)</t>
         </is>
       </c>
-      <c r="G28" s="28" t="inlineStr">
+      <c r="G28" s="31" t="inlineStr">
         <is>
           <t>TO_NUMBER(REPLACE(A.LOANRATE, ',', '') DEFAULT NULL ON CONVERSION ERROR)</t>
         </is>
       </c>
-      <c r="H28" s="28" t="inlineStr">
+      <c r="H28" s="31" t="inlineStr">
         <is>
           <t>TO_NUMBER(REPLACE(A.LOANRATE, ',', '') DEFAULT NULL ON CONVERSION ERROR)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="105" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
           <t>TYPES_OF_COLLATERALS</t>
@@ -1470,33 +1481,33 @@
           <t>Loại tài sản bảo đảm (tổng hợp)</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>Phục vụ trực tiếp BC3.TYPES_OF_COLLATERALS — đúng nguyên văn SRS BC3 (UNION NO_CERTI/TYPE_VEHICLE/TYPE1/DESCRIBE của 4 bảng grid), dựng sẵn tại ETL để tránh report phải tự xử lý NULL rải rác. Áp dụng theo COLLATERAL_TYPE_CODE: REALESTATE→CERTIFICATE_NO, TRANSPORT→VEHICLE_TYPE, VALPAPER→VALPAPER_TYPE, OTHER→DESCRIPTION</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>CERTIFICATE_NO (cùng dòng)</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="31" t="inlineStr">
         <is>
           <t>VEHICLE_TYPE (cùng dòng)</t>
         </is>
       </c>
-      <c r="G29" s="28" t="inlineStr">
+      <c r="G29" s="31" t="inlineStr">
         <is>
           <t>VALPAPER_TYPE (cùng dòng)</t>
         </is>
       </c>
-      <c r="H29" s="28" t="inlineStr">
+      <c r="H29" s="31" t="inlineStr">
         <is>
           <t>DESCRIPTION (cùng dòng)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
           <t>VEHICLE_TYPE</t>
@@ -1512,33 +1523,33 @@
           <t>Loại phương tiện vận tải</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D30" s="54" t="inlineStr">
         <is>
           <t>Loại phương tiện vận tải. Chỉ có ở khối TRANSPORT — NULL ở 3 khối còn lại</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="31" t="inlineStr">
         <is>
           <t>A.TYPE_VEHICLE</t>
         </is>
       </c>
-      <c r="G30" s="28" t="inlineStr">
+      <c r="G30" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="H30" s="28" t="inlineStr">
+      <c r="H30" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
           <t>BRAND</t>
@@ -1554,33 +1565,33 @@
           <t>Hãng phương tiện</t>
         </is>
       </c>
-      <c r="D31" s="27" t="inlineStr">
+      <c r="D31" s="54" t="inlineStr">
         <is>
           <t>Hãng của phương tiện vận tải. Chỉ có ở khối TRANSPORT — NULL ở 3 khối còn lại</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="31" t="inlineStr">
         <is>
           <t>A.BRAND</t>
         </is>
       </c>
-      <c r="G31" s="28" t="inlineStr">
+      <c r="G31" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="H31" s="28" t="inlineStr">
+      <c r="H31" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
           <t>CONTROL_POSTER</t>
@@ -1596,27 +1607,27 @@
           <t>Biển số kiểm soát</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
         <is>
           <t>Biển số kiểm soát của phương tiện. Chỉ có ở khối TRANSPORT — NULL ở 3 khối còn lại</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="31" t="inlineStr">
         <is>
           <t>A.CONTROL_POSTER</t>
         </is>
       </c>
-      <c r="G32" s="28" t="inlineStr">
+      <c r="G32" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="H32" s="28" t="inlineStr">
+      <c r="H32" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -1638,33 +1649,33 @@
           <t>Loại giấy tờ có giá</t>
         </is>
       </c>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="D33" s="54" t="inlineStr">
         <is>
           <t>Loại giấy tờ có giá. Chỉ có ở khối VALPAPER — NULL ở 3 khối còn lại</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="F33" s="28" t="inlineStr">
+      <c r="F33" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="G33" s="31" t="inlineStr">
         <is>
           <t>A.TYPE1</t>
         </is>
       </c>
-      <c r="H33" s="28" t="inlineStr">
+      <c r="H33" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="28" t="inlineStr">
         <is>
           <t>NUMBERSIGN</t>
@@ -1680,38 +1691,37 @@
           <t>Số hiệu giấy tờ có giá</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
         <is>
           <t>Số hiệu giấy tờ có giá. Chỉ có ở khối VALPAPER — NULL ở 3 khối còn lại. Cũng là căn cứ cho cờ BC1.TSBD_GTCG (NUMBERSIGN IS NOT NULL → 'YES')</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="F34" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="G34" s="31" t="inlineStr">
         <is>
           <t>A.NUMBERSIGN</t>
         </is>
       </c>
-      <c r="H34" s="28" t="inlineStr">
+      <c r="H34" s="31" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="51" customHeight="1"/>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="10" t="n"/>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
-      <c r="D36" s="54" t="inlineStr">
+      <c r="D36" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
@@ -1721,11 +1731,11 @@
       <c r="G36" s="10" t="n"/>
       <c r="H36" s="10" t="n"/>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="25" t="n"/>
       <c r="C37" s="51" t="n"/>
-      <c r="D37" s="8" t="n"/>
+      <c r="D37" s="54" t="n"/>
       <c r="E37" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
@@ -1747,11 +1757,11 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="150" customHeight="1">
+    <row r="38" ht="90" customHeight="1">
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="25" t="n"/>
       <c r="C38" s="51" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="54" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="inlineStr">
         <is>
@@ -1765,124 +1775,6 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="34" customHeight="1"/>
-    <row r="40" ht="34" customHeight="1"/>
-    <row r="41" ht="34" customHeight="1"/>
-    <row r="42" ht="17" customHeight="1"/>
-    <row r="43" ht="34" customHeight="1"/>
-    <row r="44" ht="17" customHeight="1"/>
-    <row r="45" ht="85" customHeight="1"/>
-    <row r="46" ht="34" customHeight="1"/>
-    <row r="47" ht="17" customHeight="1"/>
-    <row r="48" ht="17" customHeight="1"/>
-    <row r="49" ht="17" customHeight="1"/>
-    <row r="50" ht="51" customHeight="1"/>
-    <row r="51" ht="51" customHeight="1"/>
-    <row r="52" ht="34" customHeight="1"/>
-    <row r="53" ht="34" customHeight="1"/>
-    <row r="54" ht="34" customHeight="1"/>
-    <row r="55" ht="34" customHeight="1"/>
-    <row r="56" ht="68" customHeight="1"/>
-    <row r="57" ht="51" customHeight="1"/>
-    <row r="58" ht="34" customHeight="1"/>
-    <row r="59" ht="17" customHeight="1"/>
-    <row r="60" ht="34" customHeight="1"/>
-    <row r="61" ht="17" customHeight="1"/>
-    <row r="62" ht="85" customHeight="1"/>
-    <row r="63" ht="85" customHeight="1"/>
-    <row r="64" ht="34" customHeight="1"/>
-    <row r="65" ht="17" customHeight="1"/>
-    <row r="66" ht="34" customHeight="1"/>
-    <row r="67" ht="51" customHeight="1"/>
-    <row r="68" ht="51" customHeight="1"/>
-    <row r="69" ht="51" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="71" ht="34" customHeight="1"/>
-    <row r="72" ht="34" customHeight="1"/>
-    <row r="73" ht="34" customHeight="1"/>
-    <row r="74" ht="34" customHeight="1"/>
-    <row r="75" ht="34" customHeight="1"/>
-    <row r="76" ht="34" customHeight="1"/>
-    <row r="77" ht="51" customHeight="1"/>
-    <row r="78" ht="34" customHeight="1"/>
-    <row r="79" ht="51" customHeight="1"/>
-    <row r="80" ht="17" customHeight="1"/>
-    <row r="81" ht="17" customHeight="1"/>
-    <row r="82" ht="17" customHeight="1"/>
-    <row r="83" ht="17" customHeight="1"/>
-    <row r="84" ht="17" customHeight="1"/>
-    <row r="85" ht="17" customHeight="1"/>
-    <row r="86" ht="17" customHeight="1"/>
-    <row r="87" ht="17" customHeight="1"/>
-    <row r="88" ht="17" customHeight="1"/>
-    <row r="89" ht="17" customHeight="1"/>
-    <row r="90" ht="34" customHeight="1"/>
-    <row r="91" ht="17" customHeight="1"/>
-    <row r="92" ht="17" customHeight="1"/>
-    <row r="93" ht="17" customHeight="1"/>
-    <row r="94" ht="17" customHeight="1"/>
-    <row r="95" ht="17" customHeight="1"/>
-    <row r="96" ht="17" customHeight="1"/>
-    <row r="97" ht="17" customHeight="1"/>
-    <row r="100" ht="187" customHeight="1"/>
-    <row r="101" ht="17" customHeight="1"/>
-    <row r="102" ht="17" customHeight="1"/>
-    <row r="103" ht="17" customHeight="1"/>
-    <row r="104" ht="17" customHeight="1"/>
-    <row r="105" ht="17" customHeight="1"/>
-    <row r="106" ht="17" customHeight="1"/>
-    <row r="107" ht="17" customHeight="1"/>
-    <row r="108" ht="17" customHeight="1"/>
-    <row r="109" ht="17" customHeight="1"/>
-    <row r="110" ht="17" customHeight="1"/>
-    <row r="111" ht="17" customHeight="1"/>
-    <row r="112" ht="17" customHeight="1"/>
-    <row r="113" ht="17" customHeight="1"/>
-    <row r="114" ht="17" customHeight="1"/>
-    <row r="115" ht="17" customHeight="1"/>
-    <row r="116" ht="17" customHeight="1"/>
-    <row r="117" ht="17" customHeight="1"/>
-    <row r="118" ht="17" customHeight="1"/>
-    <row r="119" ht="17" customHeight="1"/>
-    <row r="120" ht="68" customHeight="1"/>
-    <row r="121" ht="51" customHeight="1"/>
-    <row r="122" ht="34" customHeight="1"/>
-    <row r="123" ht="153" customHeight="1"/>
-    <row r="124" ht="17" customHeight="1"/>
-    <row r="125" ht="17" customHeight="1"/>
-    <row r="132" ht="60" customHeight="1"/>
-    <row r="133" ht="17" customHeight="1"/>
-    <row r="134" ht="17" customHeight="1"/>
-    <row r="135" ht="17" customHeight="1"/>
-    <row r="136" ht="17" customHeight="1"/>
-    <row r="137" ht="51" customHeight="1"/>
-    <row r="138" ht="45" customHeight="1"/>
-    <row r="139" ht="120" customHeight="1"/>
-    <row r="141" ht="384" customHeight="1"/>
-    <row r="143" ht="34" customHeight="1"/>
-    <row r="148" ht="119" customHeight="1"/>
-    <row r="149" ht="17" customHeight="1"/>
-    <row r="150" ht="17" customHeight="1"/>
-    <row r="151" ht="17" customHeight="1"/>
-    <row r="152" ht="51" customHeight="1"/>
-    <row r="153" ht="34" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1"/>
-    <row r="155" ht="17" customHeight="1"/>
-    <row r="157" ht="119" customHeight="1"/>
-    <row r="158" ht="17" customHeight="1"/>
-    <row r="159" ht="17" customHeight="1"/>
-    <row r="160" ht="17" customHeight="1"/>
-    <row r="161" ht="17" customHeight="1"/>
-    <row r="162" ht="17" customHeight="1"/>
-    <row r="163" ht="17" customHeight="1"/>
-    <row r="164" ht="17" customHeight="1"/>
-    <row r="165" ht="17" customHeight="1"/>
-    <row r="166" ht="34" customHeight="1"/>
-    <row r="167" ht="34" customHeight="1"/>
-    <row r="168" ht="16" customHeight="1"/>
-    <row r="169" ht="17" customHeight="1"/>
-    <row r="170" ht="17" customHeight="1"/>
-    <row r="2480" customFormat="1" s="19"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
